--- a/artfynd/A 19521-2023 artfynd.xlsx
+++ b/artfynd/A 19521-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 19521-2023 artfynd.xlsx
+++ b/artfynd/A 19521-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1148,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113168459</v>
+        <v>113169865</v>
       </c>
       <c r="B6" t="n">
-        <v>78246</v>
+        <v>56478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,38 +1160,43 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Naggen SO, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556787</v>
+        <v>556659</v>
       </c>
       <c r="R6" t="n">
-        <v>6897348</v>
+        <v>6897144</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1226,6 +1231,11 @@
           <t>2022-08-04</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Uppflygande</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1252,453 +1262,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>113125165</v>
-      </c>
-      <c r="B7" t="n">
-        <v>94950</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>2869</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Bollvitmossa</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Sphagnum wulfianum</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Naggen SO, Hls</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>556868</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6897426</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Bjuråker</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN, Ambjorn Johansson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>113169865</v>
-      </c>
-      <c r="B8" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Naggen SO, Hls</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>556659</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6897144</v>
-      </c>
-      <c r="S8" t="n">
-        <v>10</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Bjuråker</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Uppflygande</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN, Ambjorn Johansson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>113168118</v>
-      </c>
-      <c r="B9" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Naggen SO, Hls</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>556754</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6897371</v>
-      </c>
-      <c r="S9" t="n">
-        <v>10</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Bjuråker</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På sälg som det nyligen avverkats omkring, kommer troligen att dö.</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN, Ambjorn Johansson</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>113169715</v>
-      </c>
-      <c r="B10" t="n">
-        <v>58078</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>208249</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Vanlig groda</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Rana temporaria</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Naggen SO, Hls</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>556794</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6897561</v>
-      </c>
-      <c r="S10" t="n">
-        <v>10</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Hudiksvall</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Hälsingland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Bjuråker</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>MIKAELA BOLTENSTERN, Ambjorn Johansson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19521-2023 artfynd.xlsx
+++ b/artfynd/A 19521-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105545632</v>
+        <v>105545700</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1588</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bodsjöåsen, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>556754.358001222</v>
+        <v>556624</v>
       </c>
       <c r="R2" t="n">
-        <v>6897370.56018041</v>
+        <v>6897274</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,32 +746,18 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På sälg som det nyligen avverkats omkring, kommer troligen att dö.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -796,15 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105546059</v>
+        <v>105545369</v>
       </c>
       <c r="B3" t="n">
-        <v>57577</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,38 +791,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bodsjöåsen, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>556794.1497243921</v>
+        <v>556868</v>
       </c>
       <c r="R3" t="n">
-        <v>6897561.19946485</v>
+        <v>6897426</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,22 +845,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-08-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-08-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,37 +881,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105545369</v>
+        <v>105545674</v>
       </c>
       <c r="B4" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -956,10 +916,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>556868.4124778175</v>
+        <v>556942</v>
       </c>
       <c r="R4" t="n">
-        <v>6897426.161133094</v>
+        <v>6897479</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,19 +949,9 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,37 +982,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105545648</v>
+        <v>105545676</v>
       </c>
       <c r="B5" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1072,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>556786.5288777561</v>
+        <v>556530</v>
       </c>
       <c r="R5" t="n">
-        <v>6897347.763828881</v>
+        <v>6897174</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,19 +1050,9 @@
           <t>2022-08-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113169865</v>
+        <v>105545612</v>
       </c>
       <c r="B6" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,39 +1094,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6434</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Naggen SO, Hls</t>
+          <t>Bodsjöåsen, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>556659</v>
+        <v>556623</v>
       </c>
       <c r="R6" t="n">
-        <v>6897144</v>
+        <v>6897272</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,17 +1148,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-08-04</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-08-04</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Uppflygande</t>
+          <t>2022-08-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,24 +1164,1821 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>Lisa Sandberg</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>MIKAELA BOLTENSTERN</t>
+          <t>Lisa Sandberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>MIKAELA BOLTENSTERN, Ambjorn Johansson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>105545598</v>
+      </c>
+      <c r="B7" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bodsjöåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>556715</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6897199</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>105545648</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bodsjöåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>556787</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6897348</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>105545649</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bodsjöåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>556568</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6897317</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>105545632</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bodsjöåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>556754</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6897371</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På sälg som det nyligen avverkats omkring, kommer troligen att dö.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>105545414</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bodsjöåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>556659</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6897144</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Uppflygande</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>105545415</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bodsjöåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>556562</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6897116</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>105545417</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bodsjöåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>556650</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6897290</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>105545788</v>
+      </c>
+      <c r="B14" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bodsjöåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>556551</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6897196</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>105545424</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bodsjöåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>556718</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6897196</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Uppflygande</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>105545779</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bodsjöåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>556767</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6897311</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>105545780</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bodsjöåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>556551</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6897196</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>105545781</v>
+      </c>
+      <c r="B18" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bodsjöåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>556470</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6897361</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>105546059</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bodsjöåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>556794</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6897561</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2022-08-03</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2022-08-03</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>105545491</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bodsjöåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>556557</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6897113</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>105545500</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bodsjöåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>556784</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6897548</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2022-08-03</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2022-08-03</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt spridd</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>105545501</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bodsjöåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>556615</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6897471</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2022-08-03</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2022-08-03</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>105545618</v>
+      </c>
+      <c r="B23" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bodsjöåsen, Hls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>556566</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6897317</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Hudiksvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Bjuråker</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-08-02</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
